--- a/artfynd/A 38124-2024 artfynd.xlsx
+++ b/artfynd/A 38124-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515965</v>
+        <v>121515956</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594656</v>
+        <v>594351</v>
       </c>
       <c r="R2" t="n">
-        <v>7182682</v>
+        <v>7182826</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515958</v>
+        <v>121515961</v>
       </c>
       <c r="B3" t="n">
-        <v>57465</v>
+        <v>57354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,20 +799,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,14 +820,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594412</v>
+        <v>594616</v>
       </c>
       <c r="R3" t="n">
-        <v>7182812</v>
+        <v>7182687</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515957</v>
+        <v>121515965</v>
       </c>
       <c r="B4" t="n">
         <v>57370</v>
@@ -958,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594351</v>
+        <v>594656</v>
       </c>
       <c r="R4" t="n">
-        <v>7182823</v>
+        <v>7182682</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515964</v>
+        <v>121515958</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>57465</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,20 +1033,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1063,10 +1054,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594656</v>
+        <v>594412</v>
       </c>
       <c r="R5" t="n">
-        <v>7182682</v>
+        <v>7182812</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,7 +1142,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515963</v>
+        <v>121515960</v>
       </c>
       <c r="B6" t="n">
         <v>57354</v>
@@ -1183,7 +1178,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594653</v>
+        <v>594545</v>
       </c>
       <c r="R6" t="n">
-        <v>7182684</v>
+        <v>7182709</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,7 +1259,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515966</v>
+        <v>121515962</v>
       </c>
       <c r="B7" t="n">
         <v>57354</v>
@@ -1309,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594660</v>
+        <v>594617</v>
       </c>
       <c r="R7" t="n">
-        <v>7182687</v>
+        <v>7182680</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1344,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515956</v>
+        <v>121515957</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>57370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,24 +1392,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -1424,7 +1424,7 @@
         <v>594351</v>
       </c>
       <c r="R8" t="n">
-        <v>7182826</v>
+        <v>7182823</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1493,7 +1493,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515960</v>
+        <v>121515964</v>
       </c>
       <c r="B9" t="n">
         <v>57354</v>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594545</v>
+        <v>594656</v>
       </c>
       <c r="R9" t="n">
-        <v>7182709</v>
+        <v>7182682</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1727,7 +1727,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515961</v>
+        <v>121515963</v>
       </c>
       <c r="B11" t="n">
         <v>57354</v>
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594616</v>
+        <v>594653</v>
       </c>
       <c r="R11" t="n">
-        <v>7182687</v>
+        <v>7182684</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,7 +1844,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515962</v>
+        <v>121515966</v>
       </c>
       <c r="B12" t="n">
         <v>57354</v>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594617</v>
+        <v>594660</v>
       </c>
       <c r="R12" t="n">
-        <v>7182680</v>
+        <v>7182687</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 38124-2024 artfynd.xlsx
+++ b/artfynd/A 38124-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515956</v>
+        <v>121515960</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594351</v>
+        <v>594545</v>
       </c>
       <c r="R2" t="n">
-        <v>7182826</v>
+        <v>7182709</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515961</v>
+        <v>121515957</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +828,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594616</v>
+        <v>594351</v>
       </c>
       <c r="R3" t="n">
-        <v>7182687</v>
+        <v>7182823</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515965</v>
+        <v>121515956</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594656</v>
+        <v>594351</v>
       </c>
       <c r="R4" t="n">
-        <v>7182682</v>
+        <v>7182826</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515958</v>
+        <v>121515966</v>
       </c>
       <c r="B5" t="n">
-        <v>57465</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,20 +1033,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,14 +1054,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594412</v>
+        <v>594660</v>
       </c>
       <c r="R5" t="n">
-        <v>7182812</v>
+        <v>7182687</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515960</v>
+        <v>121515958</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>57466</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,20 +1150,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1175,10 +1171,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594545</v>
+        <v>594412</v>
       </c>
       <c r="R6" t="n">
-        <v>7182709</v>
+        <v>7182812</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515962</v>
+        <v>121515963</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594617</v>
+        <v>594653</v>
       </c>
       <c r="R7" t="n">
-        <v>7182680</v>
+        <v>7182684</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515957</v>
+        <v>121515962</v>
       </c>
       <c r="B8" t="n">
-        <v>57370</v>
+        <v>57355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,16 +1392,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594351</v>
+        <v>594617</v>
       </c>
       <c r="R8" t="n">
-        <v>7182823</v>
+        <v>7182680</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,7 +1496,7 @@
         <v>121515964</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515959</v>
+        <v>121515965</v>
       </c>
       <c r="B10" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594546</v>
+        <v>594656</v>
       </c>
       <c r="R10" t="n">
-        <v>7182717</v>
+        <v>7182682</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515963</v>
+        <v>121515961</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594653</v>
+        <v>594616</v>
       </c>
       <c r="R11" t="n">
-        <v>7182684</v>
+        <v>7182687</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515966</v>
+        <v>121515959</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>57371</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,16 +1860,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594660</v>
+        <v>594546</v>
       </c>
       <c r="R12" t="n">
-        <v>7182687</v>
+        <v>7182717</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 38124-2024 artfynd.xlsx
+++ b/artfynd/A 38124-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515960</v>
+        <v>121515966</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594545</v>
+        <v>594660</v>
       </c>
       <c r="R2" t="n">
-        <v>7182709</v>
+        <v>7182687</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515957</v>
+        <v>121515959</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594351</v>
+        <v>594546</v>
       </c>
       <c r="R3" t="n">
-        <v>7182823</v>
+        <v>7182717</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515956</v>
+        <v>121515963</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594351</v>
+        <v>594653</v>
       </c>
       <c r="R4" t="n">
-        <v>7182826</v>
+        <v>7182684</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515966</v>
+        <v>121515962</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594660</v>
+        <v>594617</v>
       </c>
       <c r="R5" t="n">
-        <v>7182687</v>
+        <v>7182680</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1146,7 @@
         <v>121515958</v>
       </c>
       <c r="B6" t="n">
-        <v>57466</v>
+        <v>57467</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1259,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515963</v>
+        <v>121515965</v>
       </c>
       <c r="B7" t="n">
-        <v>57355</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,16 +1280,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1295,7 +1300,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594653</v>
+        <v>594656</v>
       </c>
       <c r="R7" t="n">
-        <v>7182684</v>
+        <v>7182682</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515962</v>
+        <v>121515961</v>
       </c>
       <c r="B8" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594617</v>
+        <v>594616</v>
       </c>
       <c r="R8" t="n">
-        <v>7182680</v>
+        <v>7182687</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1456,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515964</v>
+        <v>121515957</v>
       </c>
       <c r="B9" t="n">
-        <v>57355</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,16 +1514,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1538,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594656</v>
+        <v>594351</v>
       </c>
       <c r="R9" t="n">
-        <v>7182682</v>
+        <v>7182823</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515965</v>
+        <v>121515956</v>
       </c>
       <c r="B10" t="n">
-        <v>57371</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,39 +1631,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594656</v>
+        <v>594351</v>
       </c>
       <c r="R10" t="n">
-        <v>7182682</v>
+        <v>7182826</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515961</v>
+        <v>121515960</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594616</v>
+        <v>594545</v>
       </c>
       <c r="R11" t="n">
-        <v>7182687</v>
+        <v>7182709</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515959</v>
+        <v>121515964</v>
       </c>
       <c r="B12" t="n">
-        <v>57371</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,16 +1860,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594546</v>
+        <v>594656</v>
       </c>
       <c r="R12" t="n">
-        <v>7182717</v>
+        <v>7182682</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 38124-2024 artfynd.xlsx
+++ b/artfynd/A 38124-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515966</v>
+        <v>121515959</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594660</v>
+        <v>594546</v>
       </c>
       <c r="R2" t="n">
-        <v>7182687</v>
+        <v>7182717</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515959</v>
+        <v>121515963</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,7 +828,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594546</v>
+        <v>594653</v>
       </c>
       <c r="R3" t="n">
-        <v>7182717</v>
+        <v>7182684</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515963</v>
+        <v>121515966</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594653</v>
+        <v>594660</v>
       </c>
       <c r="R4" t="n">
-        <v>7182684</v>
+        <v>7182687</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515962</v>
+        <v>121515961</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594617</v>
+        <v>594616</v>
       </c>
       <c r="R5" t="n">
-        <v>7182680</v>
+        <v>7182687</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515958</v>
+        <v>121515964</v>
       </c>
       <c r="B6" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,20 +1155,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1176,14 +1176,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594412</v>
+        <v>594656</v>
       </c>
       <c r="R6" t="n">
-        <v>7182812</v>
+        <v>7182682</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515965</v>
+        <v>121515956</v>
       </c>
       <c r="B7" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,39 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594656</v>
+        <v>594351</v>
       </c>
       <c r="R7" t="n">
-        <v>7182682</v>
+        <v>7182826</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1344,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515961</v>
+        <v>121515965</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,16 +1388,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1417,7 +1408,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594616</v>
+        <v>594656</v>
       </c>
       <c r="R8" t="n">
-        <v>7182687</v>
+        <v>7182682</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1461,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1615,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515956</v>
+        <v>121515962</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,34 +1622,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594351</v>
+        <v>594617</v>
       </c>
       <c r="R10" t="n">
-        <v>7182826</v>
+        <v>7182680</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1690,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1844,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515964</v>
+        <v>121515958</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>57467</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,20 +1852,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1877,10 +1873,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594656</v>
+        <v>594412</v>
       </c>
       <c r="R12" t="n">
-        <v>7182682</v>
+        <v>7182812</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 38124-2024 artfynd.xlsx
+++ b/artfynd/A 38124-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515959</v>
+        <v>121515961</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594546</v>
+        <v>594616</v>
       </c>
       <c r="R2" t="n">
-        <v>7182717</v>
+        <v>7182687</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515963</v>
+        <v>121515964</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -828,7 +828,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594653</v>
+        <v>594656</v>
       </c>
       <c r="R3" t="n">
-        <v>7182684</v>
+        <v>7182682</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515966</v>
+        <v>121515960</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -945,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594660</v>
+        <v>594545</v>
       </c>
       <c r="R4" t="n">
-        <v>7182687</v>
+        <v>7182709</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515961</v>
+        <v>121515959</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,7 +1062,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594616</v>
+        <v>594546</v>
       </c>
       <c r="R5" t="n">
-        <v>7182687</v>
+        <v>7182717</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515964</v>
+        <v>121515958</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>57467</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,20 +1155,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1176,10 +1176,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594656</v>
+        <v>594412</v>
       </c>
       <c r="R6" t="n">
-        <v>7182682</v>
+        <v>7182812</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515956</v>
+        <v>121515965</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,34 +1280,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594351</v>
+        <v>594656</v>
       </c>
       <c r="R7" t="n">
-        <v>7182826</v>
+        <v>7182682</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1335,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515965</v>
+        <v>121515956</v>
       </c>
       <c r="B8" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,39 +1397,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594656</v>
+        <v>594351</v>
       </c>
       <c r="R8" t="n">
-        <v>7182682</v>
+        <v>7182826</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1606,7 +1610,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515962</v>
+        <v>121515966</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1651,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594617</v>
+        <v>594660</v>
       </c>
       <c r="R10" t="n">
-        <v>7182680</v>
+        <v>7182687</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1686,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,7 +1727,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515960</v>
+        <v>121515963</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1759,7 +1763,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1768,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594545</v>
+        <v>594653</v>
       </c>
       <c r="R11" t="n">
-        <v>7182709</v>
+        <v>7182684</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1803,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515958</v>
+        <v>121515962</v>
       </c>
       <c r="B12" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,20 +1856,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1873,14 +1877,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594412</v>
+        <v>594617</v>
       </c>
       <c r="R12" t="n">
-        <v>7182812</v>
+        <v>7182680</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 38124-2024 artfynd.xlsx
+++ b/artfynd/A 38124-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515961</v>
+        <v>121515963</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594616</v>
+        <v>594653</v>
       </c>
       <c r="R2" t="n">
-        <v>7182687</v>
+        <v>7182684</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515964</v>
+        <v>121515958</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>57467</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,20 +804,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,10 +825,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594656</v>
+        <v>594412</v>
       </c>
       <c r="R3" t="n">
-        <v>7182682</v>
+        <v>7182812</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515960</v>
+        <v>121515966</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -945,7 +949,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594545</v>
+        <v>594660</v>
       </c>
       <c r="R4" t="n">
-        <v>7182709</v>
+        <v>7182687</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515959</v>
+        <v>121515960</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1071,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594546</v>
+        <v>594545</v>
       </c>
       <c r="R5" t="n">
-        <v>7182717</v>
+        <v>7182709</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1143,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515958</v>
+        <v>121515959</v>
       </c>
       <c r="B6" t="n">
-        <v>57467</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,20 +1159,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1176,14 +1180,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594412</v>
+        <v>594546</v>
       </c>
       <c r="R6" t="n">
-        <v>7182812</v>
+        <v>7182717</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,7 +1264,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515965</v>
+        <v>121515957</v>
       </c>
       <c r="B7" t="n">
         <v>57372</v>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594656</v>
+        <v>594351</v>
       </c>
       <c r="R7" t="n">
-        <v>7182682</v>
+        <v>7182823</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515956</v>
+        <v>121515964</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,34 +1397,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594351</v>
+        <v>594656</v>
       </c>
       <c r="R8" t="n">
-        <v>7182826</v>
+        <v>7182682</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1456,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,7 +1498,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515957</v>
+        <v>121515965</v>
       </c>
       <c r="B9" t="n">
         <v>57372</v>
@@ -1538,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594351</v>
+        <v>594656</v>
       </c>
       <c r="R9" t="n">
-        <v>7182823</v>
+        <v>7182682</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515966</v>
+        <v>121515956</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,39 +1631,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594660</v>
+        <v>594351</v>
       </c>
       <c r="R10" t="n">
-        <v>7182687</v>
+        <v>7182826</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,7 +1727,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515963</v>
+        <v>121515962</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594653</v>
+        <v>594617</v>
       </c>
       <c r="R11" t="n">
-        <v>7182684</v>
+        <v>7182680</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,7 +1844,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515962</v>
+        <v>121515961</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594617</v>
+        <v>594616</v>
       </c>
       <c r="R12" t="n">
-        <v>7182680</v>
+        <v>7182687</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 38124-2024 artfynd.xlsx
+++ b/artfynd/A 38124-2024 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515958</v>
+        <v>121515959</v>
       </c>
       <c r="B4" t="n">
-        <v>57468</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,20 +921,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -942,14 +942,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594412</v>
+        <v>594546</v>
       </c>
       <c r="R4" t="n">
-        <v>7182812</v>
+        <v>7182717</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1147,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515956</v>
+        <v>121515958</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57468</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,38 +1155,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594351</v>
+        <v>594412</v>
       </c>
       <c r="R6" t="n">
-        <v>7182826</v>
+        <v>7182812</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1222,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515961</v>
+        <v>121515957</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,16 +1280,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1295,7 +1300,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594616</v>
+        <v>594351</v>
       </c>
       <c r="R7" t="n">
-        <v>7182687</v>
+        <v>7182823</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515960</v>
+        <v>121515956</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,39 +1397,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594545</v>
+        <v>594351</v>
       </c>
       <c r="R8" t="n">
-        <v>7182709</v>
+        <v>7182826</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515957</v>
+        <v>121515961</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,16 +1743,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594351</v>
+        <v>594616</v>
       </c>
       <c r="R11" t="n">
-        <v>7182823</v>
+        <v>7182687</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515959</v>
+        <v>121515960</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,16 +1860,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594546</v>
+        <v>594545</v>
       </c>
       <c r="R12" t="n">
-        <v>7182717</v>
+        <v>7182709</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 38124-2024 artfynd.xlsx
+++ b/artfynd/A 38124-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515964</v>
+        <v>121515959</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594656</v>
+        <v>594546</v>
       </c>
       <c r="R3" t="n">
-        <v>7182682</v>
+        <v>7182717</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515959</v>
+        <v>121515964</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594546</v>
+        <v>594656</v>
       </c>
       <c r="R4" t="n">
-        <v>7182717</v>
+        <v>7182682</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 38124-2024 artfynd.xlsx
+++ b/artfynd/A 38124-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515963</v>
+        <v>121515966</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594653</v>
+        <v>594660</v>
       </c>
       <c r="R2" t="n">
-        <v>7182684</v>
+        <v>7182687</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515959</v>
+        <v>121515962</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,7 +828,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594546</v>
+        <v>594617</v>
       </c>
       <c r="R3" t="n">
-        <v>7182717</v>
+        <v>7182680</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515964</v>
+        <v>121515963</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -945,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594656</v>
+        <v>594653</v>
       </c>
       <c r="R4" t="n">
-        <v>7182682</v>
+        <v>7182684</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515966</v>
+        <v>121515964</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1062,7 +1062,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594660</v>
+        <v>594656</v>
       </c>
       <c r="R5" t="n">
-        <v>7182687</v>
+        <v>7182682</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515958</v>
+        <v>121515957</v>
       </c>
       <c r="B6" t="n">
-        <v>57468</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,20 +1155,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1176,14 +1176,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594412</v>
+        <v>594351</v>
       </c>
       <c r="R6" t="n">
-        <v>7182812</v>
+        <v>7182823</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515957</v>
+        <v>121515965</v>
       </c>
       <c r="B7" t="n">
         <v>57373</v>
@@ -1309,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594351</v>
+        <v>594656</v>
       </c>
       <c r="R7" t="n">
-        <v>7182823</v>
+        <v>7182682</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1344,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515956</v>
+        <v>121515958</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>57468</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,38 +1389,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594351</v>
+        <v>594412</v>
       </c>
       <c r="R8" t="n">
-        <v>7182826</v>
+        <v>7182812</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1456,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515962</v>
+        <v>121515956</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,39 +1514,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594617</v>
+        <v>594351</v>
       </c>
       <c r="R9" t="n">
-        <v>7182680</v>
+        <v>7182826</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515965</v>
+        <v>121515960</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594656</v>
+        <v>594545</v>
       </c>
       <c r="R10" t="n">
-        <v>7182682</v>
+        <v>7182709</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1844,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515960</v>
+        <v>121515959</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,16 +1860,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594545</v>
+        <v>594546</v>
       </c>
       <c r="R12" t="n">
-        <v>7182709</v>
+        <v>7182717</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 38124-2024 artfynd.xlsx
+++ b/artfynd/A 38124-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515962</v>
+        <v>121515960</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -828,7 +828,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594617</v>
+        <v>594545</v>
       </c>
       <c r="R3" t="n">
-        <v>7182680</v>
+        <v>7182709</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515964</v>
+        <v>121515958</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>57468</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,20 +1038,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,10 +1059,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594656</v>
+        <v>594412</v>
       </c>
       <c r="R5" t="n">
-        <v>7182682</v>
+        <v>7182812</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515957</v>
+        <v>121515962</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,16 +1163,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1179,7 +1183,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594351</v>
+        <v>594617</v>
       </c>
       <c r="R6" t="n">
-        <v>7182823</v>
+        <v>7182680</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515965</v>
+        <v>121515956</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,39 +1280,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594656</v>
+        <v>594351</v>
       </c>
       <c r="R7" t="n">
-        <v>7182682</v>
+        <v>7182826</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515958</v>
+        <v>121515961</v>
       </c>
       <c r="B8" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,20 +1388,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1410,14 +1409,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594412</v>
+        <v>594616</v>
       </c>
       <c r="R8" t="n">
-        <v>7182812</v>
+        <v>7182687</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1461,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515956</v>
+        <v>121515964</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,34 +1509,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594351</v>
+        <v>594656</v>
       </c>
       <c r="R9" t="n">
-        <v>7182826</v>
+        <v>7182682</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515960</v>
+        <v>121515959</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594545</v>
+        <v>594546</v>
       </c>
       <c r="R10" t="n">
-        <v>7182709</v>
+        <v>7182717</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515961</v>
+        <v>121515957</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,16 +1743,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594616</v>
+        <v>594351</v>
       </c>
       <c r="R11" t="n">
-        <v>7182687</v>
+        <v>7182823</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,7 +1844,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515959</v>
+        <v>121515965</v>
       </c>
       <c r="B12" t="n">
         <v>57373</v>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594546</v>
+        <v>594656</v>
       </c>
       <c r="R12" t="n">
-        <v>7182717</v>
+        <v>7182682</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 38124-2024 artfynd.xlsx
+++ b/artfynd/A 38124-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515966</v>
+        <v>121515957</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594660</v>
+        <v>594351</v>
       </c>
       <c r="R2" t="n">
-        <v>7182687</v>
+        <v>7182823</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515960</v>
+        <v>121515961</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -828,7 +828,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594545</v>
+        <v>594616</v>
       </c>
       <c r="R3" t="n">
-        <v>7182709</v>
+        <v>7182687</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515963</v>
+        <v>121515959</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -945,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594653</v>
+        <v>594546</v>
       </c>
       <c r="R4" t="n">
-        <v>7182684</v>
+        <v>7182717</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515958</v>
+        <v>121515966</v>
       </c>
       <c r="B5" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,20 +1038,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,14 +1059,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594412</v>
+        <v>594660</v>
       </c>
       <c r="R5" t="n">
-        <v>7182812</v>
+        <v>7182687</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515962</v>
+        <v>121515956</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,39 +1159,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594617</v>
+        <v>594351</v>
       </c>
       <c r="R6" t="n">
-        <v>7182680</v>
+        <v>7182826</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515956</v>
+        <v>121515964</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,34 +1271,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594351</v>
+        <v>594656</v>
       </c>
       <c r="R7" t="n">
-        <v>7182826</v>
+        <v>7182682</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515961</v>
+        <v>121515958</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>57468</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,20 +1384,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1409,10 +1405,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594616</v>
+        <v>594412</v>
       </c>
       <c r="R8" t="n">
-        <v>7182687</v>
+        <v>7182812</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,7 +1493,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515964</v>
+        <v>121515960</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594656</v>
+        <v>594545</v>
       </c>
       <c r="R9" t="n">
-        <v>7182682</v>
+        <v>7182709</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515959</v>
+        <v>121515963</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1646,7 +1646,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594546</v>
+        <v>594653</v>
       </c>
       <c r="R10" t="n">
-        <v>7182717</v>
+        <v>7182684</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515957</v>
+        <v>121515962</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,16 +1743,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594351</v>
+        <v>594617</v>
       </c>
       <c r="R11" t="n">
-        <v>7182823</v>
+        <v>7182680</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 38124-2024 artfynd.xlsx
+++ b/artfynd/A 38124-2024 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515959</v>
+        <v>121515964</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594546</v>
+        <v>594656</v>
       </c>
       <c r="R4" t="n">
-        <v>7182717</v>
+        <v>7182682</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515966</v>
+        <v>121515958</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>57468</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,20 +1038,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,10 +1059,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594660</v>
+        <v>594412</v>
       </c>
       <c r="R5" t="n">
-        <v>7182687</v>
+        <v>7182812</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515956</v>
+        <v>121515959</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1163,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594351</v>
+        <v>594546</v>
       </c>
       <c r="R6" t="n">
-        <v>7182826</v>
+        <v>7182717</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1264,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515964</v>
+        <v>121515960</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1300,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594656</v>
+        <v>594545</v>
       </c>
       <c r="R7" t="n">
-        <v>7182682</v>
+        <v>7182709</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1335,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515958</v>
+        <v>121515965</v>
       </c>
       <c r="B8" t="n">
-        <v>57468</v>
+        <v>57373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,20 +1393,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1405,14 +1414,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1421,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594412</v>
+        <v>594656</v>
       </c>
       <c r="R8" t="n">
-        <v>7182812</v>
+        <v>7182682</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1456,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,7 +1498,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121515960</v>
+        <v>121515962</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1529,7 +1534,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1538,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594545</v>
+        <v>594617</v>
       </c>
       <c r="R9" t="n">
-        <v>7182709</v>
+        <v>7182680</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,7 +1615,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515963</v>
+        <v>121515966</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1655,10 +1660,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594653</v>
+        <v>594660</v>
       </c>
       <c r="R10" t="n">
-        <v>7182684</v>
+        <v>7182687</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1690,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1705,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515962</v>
+        <v>121515956</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,39 +1748,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594617</v>
+        <v>594351</v>
       </c>
       <c r="R11" t="n">
-        <v>7182680</v>
+        <v>7182826</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515965</v>
+        <v>121515963</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,16 +1860,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594656</v>
+        <v>594653</v>
       </c>
       <c r="R12" t="n">
-        <v>7182682</v>
+        <v>7182684</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 38124-2024 artfynd.xlsx
+++ b/artfynd/A 38124-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515957</v>
+        <v>121515956</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -723,7 +713,7 @@
         <v>594351</v>
       </c>
       <c r="R2" t="n">
-        <v>7182823</v>
+        <v>7182826</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -792,32 +782,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515961</v>
+        <v>121515957</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,7 +813,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594616</v>
+        <v>594351</v>
       </c>
       <c r="R3" t="n">
-        <v>7182687</v>
+        <v>7182823</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,32 +894,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515964</v>
+        <v>121515959</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -954,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594656</v>
+        <v>594546</v>
       </c>
       <c r="R4" t="n">
-        <v>7182682</v>
+        <v>7182717</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515958</v>
+        <v>121515965</v>
       </c>
       <c r="B5" t="n">
-        <v>57468</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,16 +1017,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,14 +1034,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594412</v>
+        <v>594656</v>
       </c>
       <c r="R5" t="n">
-        <v>7182812</v>
+        <v>7182682</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1110,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,15 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515959</v>
+        <v>121515955</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,16 +1129,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1192,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594546</v>
+        <v>594302</v>
       </c>
       <c r="R6" t="n">
-        <v>7182717</v>
+        <v>7182841</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,12 +1233,7 @@
         <v>121515960</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,15 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515965</v>
+        <v>121515961</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,16 +1353,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1417,7 +1373,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594656</v>
+        <v>594616</v>
       </c>
       <c r="R8" t="n">
-        <v>7182682</v>
+        <v>7182687</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1461,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,12 +1457,7 @@
         <v>121515962</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,15 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121515966</v>
+        <v>121515963</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594660</v>
+        <v>594653</v>
       </c>
       <c r="R10" t="n">
-        <v>7182687</v>
+        <v>7182684</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1695,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,15 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121515956</v>
+        <v>121515964</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,34 +1689,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594351</v>
+        <v>594656</v>
       </c>
       <c r="R11" t="n">
-        <v>7182826</v>
+        <v>7182682</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1807,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,15 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121515963</v>
+        <v>121515966</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594653</v>
+        <v>594660</v>
       </c>
       <c r="R12" t="n">
-        <v>7182684</v>
+        <v>7182687</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1924,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,6 +1899,122 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121515958</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bullersjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>594412</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7182812</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
